--- a/Thread_3/Combined_Features_Cleaned.xlsx
+++ b/Thread_3/Combined_Features_Cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,29 +605,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NamABank</t>
+          <t>LP Bank</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02078200054754972</v>
+        <v>0.01584451251716489</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004592440705195959</v>
+        <v>0.002265774514953375</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01618955984235376</v>
+        <v>0.01357873800221151</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01858264253317826</v>
+        <v>0.01578180049154754</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004684549549069968</v>
+        <v>0.004384374179805892</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01789880902687701</v>
+        <v>0.009912396208119473</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01372200036970841</v>
+        <v>0.01002619029315764</v>
       </c>
     </row>
     <row r="7">
@@ -636,29 +636,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OCB</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02556590602183516</v>
+        <v>0.0214168039538715</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005215240820654769</v>
+        <v>-0.001879699248120301</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02035066520118039</v>
+        <v>0.0232965032019918</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01458315013188698</v>
+        <v>0.01539090840285345</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003769177111275951</v>
+        <v>0.004072117154440722</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01172876829881964</v>
+        <v>0.01685126206493126</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01002703184732752</v>
+        <v>0.01210476254074181</v>
       </c>
     </row>
     <row r="8">
@@ -667,29 +667,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PVcomBank</t>
+          <t>NamABank</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0078125</v>
+        <v>0.02078200054754972</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0008386084319776145</v>
+        <v>0.004592440705195959</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008651108431977615</v>
+        <v>0.01618955984235376</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001205118798899347</v>
+        <v>0.01858264253317826</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.004684549549069968</v>
       </c>
       <c r="H8" t="n">
-        <v>0.006993303240354343</v>
+        <v>0.01789880902687701</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002732807346417897</v>
+        <v>0.01372200036970841</v>
       </c>
     </row>
     <row r="9">
@@ -698,29 +698,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>OCB</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.008630289532293986</v>
+        <v>0.02556590602183516</v>
       </c>
       <c r="D9" t="n">
-        <v>0.006972127543482774</v>
+        <v>0.005215240820654769</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001658161988811212</v>
+        <v>0.02035066520118039</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01620397424945525</v>
+        <v>0.01458315013188698</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001937469077060461</v>
+        <v>0.003769177111275951</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003729165765536285</v>
+        <v>0.01172876829881964</v>
       </c>
       <c r="I9" t="n">
-        <v>0.007290203030684</v>
+        <v>0.01002703184732752</v>
       </c>
     </row>
     <row r="10">
@@ -729,29 +729,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Techcombank</t>
+          <t>PVcomBank</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.01005679745714137</v>
+        <v>0.0078125</v>
       </c>
       <c r="D10" t="n">
-        <v>0.003885270097677729</v>
+        <v>-0.0008386084319776145</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00617152735946364</v>
+        <v>0.008651108431977615</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01012370431447045</v>
+        <v>0.001205118798899347</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002806815392435189</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01790054778318518</v>
+        <v>0.006993303240354343</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01027702249669694</v>
+        <v>0.002732807346417897</v>
       </c>
     </row>
     <row r="11">
@@ -760,29 +760,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TPBank</t>
+          <t>SeABank</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02768076269586559</v>
+        <v>0.009687314999192724</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004628931011337521</v>
+        <v>0.004024161563863859</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02305183168452806</v>
+        <v>0.005663153435328865</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0126381519671675</v>
+        <v>0.009194541227950577</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00961918057454568</v>
+        <v>0.003255287315202559</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01512386793796684</v>
+        <v>0.01380697347915788</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01246040015989334</v>
+        <v>0.00875226734077034</v>
       </c>
     </row>
     <row r="12">
@@ -791,29 +791,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vietcombank</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.01782661782661783</v>
+        <v>0.008630289532293986</v>
       </c>
       <c r="D12" t="n">
-        <v>0.008576106393498111</v>
+        <v>0.006972127543482774</v>
       </c>
       <c r="E12" t="n">
-        <v>0.009250511433119715</v>
+        <v>0.001658161988811212</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01643843203058502</v>
+        <v>0.01620397424945525</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003420907671228114</v>
+        <v>0.001937469077060461</v>
       </c>
       <c r="H12" t="n">
-        <v>0.006779487861063511</v>
+        <v>0.003729165765536285</v>
       </c>
       <c r="I12" t="n">
-        <v>0.008879609187625547</v>
+        <v>0.007290203030684</v>
       </c>
     </row>
     <row r="13">
@@ -822,29 +822,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VietinBank</t>
+          <t>Techcombank</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02081738131699847</v>
+        <v>0.01005679745714137</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01332254660579501</v>
+        <v>0.003885270097677729</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00749483471120346</v>
+        <v>0.00617152735946364</v>
       </c>
       <c r="F13" t="n">
-        <v>0.009926079238218312</v>
+        <v>0.01012370431447045</v>
       </c>
       <c r="G13" t="n">
-        <v>0.003937835337894874</v>
+        <v>0.002806815392435189</v>
       </c>
       <c r="H13" t="n">
-        <v>0.005489066008464285</v>
+        <v>0.01790054778318518</v>
       </c>
       <c r="I13" t="n">
-        <v>0.00645099352819249</v>
+        <v>0.01027702249669694</v>
       </c>
     </row>
     <row r="14">
@@ -853,122 +853,122 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VPBank</t>
+          <t>TPBank</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02581729300336083</v>
+        <v>0.02768076269586559</v>
       </c>
       <c r="D14" t="n">
-        <v>0.004675241202632119</v>
+        <v>0.004628931011337521</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02114205180072871</v>
+        <v>0.02305183168452806</v>
       </c>
       <c r="F14" t="n">
-        <v>0.03283312984684969</v>
+        <v>0.0126381519671675</v>
       </c>
       <c r="G14" t="n">
-        <v>0.00634205170448672</v>
+        <v>0.00961918057454568</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0232744690893937</v>
+        <v>0.01512386793796684</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0208165502135767</v>
+        <v>0.01246040015989334</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ACB</t>
+          <t>Vietcombank</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.01533089858329654</v>
+        <v>0.01782661782661783</v>
       </c>
       <c r="D15" t="n">
-        <v>0.008932919201688426</v>
+        <v>0.008576106393498111</v>
       </c>
       <c r="E15" t="n">
-        <v>0.006397979381608118</v>
+        <v>0.009250511433119715</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01487515788135221</v>
+        <v>0.01643843203058502</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002250345124230294</v>
+        <v>0.003420907671228114</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01037384970555796</v>
+        <v>0.006779487861063511</v>
       </c>
       <c r="I15" t="n">
-        <v>0.009166450903713487</v>
+        <v>0.008879609187625547</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Agribank</t>
+          <t>VietinBank</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.009457602457359954</v>
+        <v>0.02081738131699847</v>
       </c>
       <c r="D16" t="n">
-        <v>0.003197904192319601</v>
+        <v>0.01332254660579501</v>
       </c>
       <c r="E16" t="n">
-        <v>0.006259698265040354</v>
+        <v>0.00749483471120346</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02083544069637586</v>
+        <v>0.009926079238218312</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00422549545788421</v>
+        <v>0.003937835337894874</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01598675405447665</v>
+        <v>0.005489066008464285</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01368256340291224</v>
+        <v>0.00645099352819249</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BIDV</t>
+          <t>VPBank</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0266270576692467</v>
+        <v>0.02581729300336083</v>
       </c>
       <c r="D17" t="n">
-        <v>0.002620316915430356</v>
+        <v>0.004675241202632119</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02400674075381634</v>
+        <v>0.02114205180072871</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01921909487788453</v>
+        <v>0.03283312984684969</v>
       </c>
       <c r="G17" t="n">
-        <v>0.00594257072675987</v>
+        <v>0.00634205170448672</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01470030110015252</v>
+        <v>0.0232744690893937</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01328732223493231</v>
+        <v>0.0208165502135767</v>
       </c>
     </row>
     <row r="18">
@@ -977,29 +977,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HDBank</t>
+          <t>ACB</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0237849385793128</v>
+        <v>0.01533089858329654</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01623454056757914</v>
+        <v>0.008932919201688426</v>
       </c>
       <c r="E18" t="n">
-        <v>0.007550398011733662</v>
+        <v>0.006397979381608118</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01282204146469637</v>
+        <v>0.01487515788135221</v>
       </c>
       <c r="G18" t="n">
-        <v>0.004004118919938602</v>
+        <v>0.002250345124230294</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01042633282711842</v>
+        <v>0.01037384970555796</v>
       </c>
       <c r="I18" t="n">
-        <v>0.009084164403917797</v>
+        <v>0.009166450903713487</v>
       </c>
     </row>
     <row r="19">
@@ -1008,29 +1008,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NCB</t>
+          <t>Agribank</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.006689584688283936</v>
+        <v>0.009457602457359954</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01217833137971628</v>
+        <v>0.003197904192319601</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.005488746691432345</v>
+        <v>0.006259698265040354</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01493013508147272</v>
+        <v>0.02083544069637586</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.00422549545788421</v>
       </c>
       <c r="H19" t="n">
-        <v>0.004388151900549343</v>
+        <v>0.01598675405447665</v>
       </c>
       <c r="I19" t="n">
-        <v>0.006439428994007354</v>
+        <v>0.01368256340291224</v>
       </c>
     </row>
     <row r="20">
@@ -1039,29 +1039,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OCB</t>
+          <t>BIDV</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01858772781902896</v>
+        <v>0.0266270576692467</v>
       </c>
       <c r="D20" t="n">
-        <v>0.008864493526857859</v>
+        <v>0.002620316915430356</v>
       </c>
       <c r="E20" t="n">
-        <v>0.009723234292171102</v>
+        <v>0.02400674075381634</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0102348966411135</v>
+        <v>0.01921909487788453</v>
       </c>
       <c r="G20" t="n">
-        <v>0.005452016218446177</v>
+        <v>0.00594257072675987</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01068281655656991</v>
+        <v>0.01470030110015252</v>
       </c>
       <c r="I20" t="n">
-        <v>0.008789909805376528</v>
+        <v>0.01328732223493231</v>
       </c>
     </row>
     <row r="21">
@@ -1070,29 +1070,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>HDBank</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01437936138718545</v>
+        <v>0.0237849385793128</v>
       </c>
       <c r="D21" t="n">
-        <v>0.006250978969166449</v>
+        <v>0.01623454056757914</v>
       </c>
       <c r="E21" t="n">
-        <v>0.008128382418019003</v>
+        <v>0.007550398011733662</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02009046177421301</v>
+        <v>0.01282204146469637</v>
       </c>
       <c r="G21" t="n">
-        <v>0.005042320421087636</v>
+        <v>0.004004118919938602</v>
       </c>
       <c r="H21" t="n">
-        <v>0.005576832627129631</v>
+        <v>0.01042633282711842</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01023653827414343</v>
+        <v>0.009084164403917797</v>
       </c>
     </row>
     <row r="22">
@@ -1101,29 +1101,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Techcombank</t>
+          <t>LP Bank</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02791568324245137</v>
+        <v>0.015724865577762</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0071174912178607</v>
+        <v>0.006881461400724822</v>
       </c>
       <c r="E22" t="n">
-        <v>0.02079819202459067</v>
+        <v>0.008843404177037174</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02769337097256719</v>
+        <v>0.009242304877239623</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01010080743370538</v>
+        <v>0.003528053167628317</v>
       </c>
       <c r="H22" t="n">
-        <v>0.01654807903506918</v>
+        <v>0.0233574449865982</v>
       </c>
       <c r="I22" t="n">
-        <v>0.01811408581378058</v>
+        <v>0.01204260101048871</v>
       </c>
     </row>
     <row r="23">
@@ -1132,29 +1132,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TPBank</t>
+          <t>NCB</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02690273014860303</v>
+        <v>0.006689584688283936</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00570112212747073</v>
+        <v>0.01217833137971628</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02120160802113229</v>
+        <v>-0.005488746691432345</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01623922916359117</v>
+        <v>0.01493013508147272</v>
       </c>
       <c r="G23" t="n">
-        <v>0.006827073504355922</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.01312118608310094</v>
+        <v>0.004388151900549343</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01206249625034934</v>
+        <v>0.006439428994007354</v>
       </c>
     </row>
     <row r="24">
@@ -1163,29 +1163,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VietAbank</t>
+          <t>OCB</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03846153846153846</v>
+        <v>0.01858772781902896</v>
       </c>
       <c r="D24" t="n">
-        <v>0.009922144406128906</v>
+        <v>0.008864493526857859</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02853939405540956</v>
+        <v>0.009723234292171102</v>
       </c>
       <c r="F24" t="n">
-        <v>0.03245441972479678</v>
+        <v>0.0102348966411135</v>
       </c>
       <c r="G24" t="n">
-        <v>0.008713405386980502</v>
+        <v>0.005452016218446177</v>
       </c>
       <c r="H24" t="n">
-        <v>0.017426810773961</v>
+        <v>0.01068281655656991</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01953154529524609</v>
+        <v>0.008789909805376528</v>
       </c>
     </row>
     <row r="25">
@@ -1194,29 +1194,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vietcombank</t>
+          <t>SeABank</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02479365593138048</v>
+        <v>0.02807661301531704</v>
       </c>
       <c r="D25" t="n">
-        <v>0.005685810955169989</v>
+        <v>0.01092620785204517</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01910784497621049</v>
+        <v>0.01715040516327187</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01722617568753728</v>
+        <v>0.01560136179860917</v>
       </c>
       <c r="G25" t="n">
-        <v>0.003561194146894737</v>
+        <v>0.002895221917712893</v>
       </c>
       <c r="H25" t="n">
-        <v>0.01460121670735087</v>
+        <v>0.01330548735346748</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01179619551392763</v>
+        <v>0.01060069035659651</v>
       </c>
     </row>
     <row r="26">
@@ -1225,29 +1225,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VietinBank</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.004154939</v>
+        <v>0.01437936138718545</v>
       </c>
       <c r="D26" t="n">
-        <v>0.005869659</v>
+        <v>0.006250978969166449</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.00171472</v>
+        <v>0.008128382418019003</v>
       </c>
       <c r="F26" t="n">
-        <v>0.005397777000379206</v>
+        <v>0.02009046177421301</v>
       </c>
       <c r="G26" t="n">
-        <v>0.001072103273131262</v>
+        <v>0.005042320421087636</v>
       </c>
       <c r="H26" t="n">
-        <v>0.002153670533762055</v>
+        <v>0.005576832627129631</v>
       </c>
       <c r="I26" t="n">
-        <v>0.002874516935757508</v>
+        <v>0.01023653827414343</v>
       </c>
     </row>
     <row r="27">
@@ -1256,28 +1256,183 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Techcombank</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.02791568324245137</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0071174912178607</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.02079819202459067</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.02769337097256719</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.01010080743370538</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.01654807903506918</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.01811408581378058</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TPBank</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.02690273014860303</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.00570112212747073</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.02120160802113229</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.01623922916359117</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.006827073504355922</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.01312118608310094</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.01206249625034934</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>VietAbank</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.009922144406128906</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.02853939405540956</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.03245441972479678</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.008713405386980502</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.017426810773961</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.01953154529524609</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Vietcombank</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.02479365593138048</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.005685810955169989</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.01910784497621049</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.01722617568753728</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.003561194146894737</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.01460121670735087</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.01179619551392763</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>VietinBank</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.004154939</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.005869659</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.00171472</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.005397777000379206</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.001072103273131262</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.002153670533762055</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.002874516935757508</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>VPBank</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C32" t="n">
         <v>0.0258111031002163</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D32" t="n">
         <v>0.006668954329057196</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E32" t="n">
         <v>0.0191421487711591</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F32" t="n">
         <v>0.01955785619332957</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G32" t="n">
         <v>0.00708724054737579</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H32" t="n">
         <v>0.01949283219996558</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I32" t="n">
         <v>0.01537930964689031</v>
       </c>
     </row>
